--- a/SN_2026.xlsx
+++ b/SN_2026.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bacfloridabank-my.sharepoint.com/personal/gmazoni_bradescobank_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gmazoni\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{3459C60D-F117-4698-B86E-0F8FC0DE2F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B55246B-76E0-4255-862F-4B3F895C7092}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BDAC55-7D37-40CC-96F5-5BF1D8444648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14565" yWindow="-16680" windowWidth="29040" windowHeight="15720" xr2:uid="{CFEFEEAF-00C2-47B7-9077-AA511B08A24B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="275">
   <si>
     <t>Note</t>
   </si>
@@ -858,6 +858,9 @@
   </si>
   <si>
     <t>XS3299614860</t>
+  </si>
+  <si>
+    <t>SN_2025_0088</t>
   </si>
 </sst>
 </file>
@@ -1375,10 +1378,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D62202-7204-4F9C-BAE9-8AFC9F55925A}">
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="66.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -4715,6 +4720,45 @@
         <v>27</v>
       </c>
     </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A89" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E89" s="15">
+        <v>46163</v>
+      </c>
+      <c r="F89" s="15"/>
+      <c r="G89" s="16">
+        <v>150000</v>
+      </c>
+      <c r="H89" s="17">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I89" s="18">
+        <f t="shared" ref="I89" si="0">H89*G89</f>
+        <v>2250</v>
+      </c>
+      <c r="J89" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="K89" s="12">
+        <f t="shared" ref="K89" si="1">HYPERLINK(
+  "https://bacfloridabank-my.sharepoint.com/personal/dguideli_bradescobank_com/Documents/SN/OK_2026/" &amp; C89 &amp; ".pdf",
+  C89
+)</f>
+        <v>0</v>
+      </c>
+      <c r="L89" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
